--- a/exports/trend_1d/ZYDUSLIFE_full_report.xlsx
+++ b/exports/trend_1d/ZYDUSLIFE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.98</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42037</v>
+        <v>42038</v>
       </c>
       <c r="H2" t="n">
-        <v>322.16</v>
+        <v>308.35</v>
       </c>
       <c r="I2" t="n">
         <v>309.095187148953</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.43</v>
+        <v>-4.69</v>
       </c>
       <c r="L2" t="n">
-        <v>1.03</v>
+        <v>5.54</v>
       </c>
       <c r="M2" t="n">
         <v>0.46</v>
       </c>
       <c r="N2" t="n">
-        <v>1.68</v>
+        <v>4.29</v>
       </c>
       <c r="O2" t="n">
         <v>0.38</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>11.59</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42048</v>
+        <v>42051</v>
       </c>
       <c r="H3" t="n">
-        <v>319.13</v>
+        <v>322.67</v>
       </c>
       <c r="I3" t="n">
         <v>322.3259444032124</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.5</v>
+        <v>-4.64</v>
       </c>
       <c r="L3" t="n">
-        <v>5.46</v>
+        <v>6.31</v>
       </c>
       <c r="M3" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="N3" t="n">
         <v>3.26</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42121</v>
+        <v>42122</v>
       </c>
       <c r="H4" t="n">
-        <v>340.36</v>
+        <v>332.34</v>
       </c>
       <c r="I4" t="n">
         <v>339.8196446580444</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K4" t="n">
-        <v>5.48</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>7.68</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>13.24</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42150</v>
+        <v>42151</v>
       </c>
       <c r="H5" t="n">
-        <v>348.88</v>
+        <v>370.86</v>
       </c>
       <c r="I5" t="n">
         <v>364.9393635396295</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.98</v>
+        <v>-11.59</v>
       </c>
       <c r="L5" t="n">
-        <v>9.039999999999999</v>
+        <v>12.53</v>
       </c>
       <c r="M5" t="n">
         <v>1.36</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>6.3</v>
       </c>
       <c r="O5" t="n">
         <v>-2.36</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.82</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42240</v>
+        <v>42241</v>
       </c>
       <c r="H6" t="n">
-        <v>368.59</v>
+        <v>364.66</v>
       </c>
       <c r="I6" t="n">
         <v>368.0258393383284</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.61</v>
+        <v>-1.67</v>
       </c>
       <c r="L6" t="n">
         <v>8.859999999999999</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>14.5</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42265</v>
+        <v>42268</v>
       </c>
       <c r="H7" t="n">
-        <v>383.89</v>
+        <v>397.83</v>
       </c>
       <c r="I7" t="n">
         <v>395.2682804091253</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.27</v>
+        <v>-9.1</v>
       </c>
       <c r="L7" t="n">
-        <v>6.95</v>
+        <v>10.39</v>
       </c>
       <c r="M7" t="n">
         <v>3.04</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.17</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42321</v>
+        <v>42324</v>
       </c>
       <c r="H8" t="n">
-        <v>412.3</v>
+        <v>396.8</v>
       </c>
       <c r="I8" t="n">
         <v>403.0957424691865</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K8" t="n">
-        <v>3.64</v>
+        <v>-0.26</v>
       </c>
       <c r="L8" t="n">
         <v>4.98</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>15.18</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42432</v>
+        <v>42433</v>
       </c>
       <c r="H9" t="n">
-        <v>333.3</v>
+        <v>337.95</v>
       </c>
       <c r="I9" t="n">
         <v>333.8917880061333</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>14.83</v>
       </c>
       <c r="L9" t="n">
         <v>7.35</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>10.41</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42457</v>
+        <v>42458</v>
       </c>
       <c r="H10" t="n">
-        <v>318.6</v>
+        <v>316.4</v>
       </c>
       <c r="I10" t="n">
         <v>317.5122174407078</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.73</v>
+        <v>-6.38</v>
       </c>
       <c r="L10" t="n">
-        <v>7.97</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>5.1</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.65</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42550</v>
+        <v>42551</v>
       </c>
       <c r="H11" t="n">
-        <v>323.3</v>
+        <v>328.2</v>
       </c>
       <c r="I11" t="n">
         <v>328.0742516637434</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.18</v>
+        <v>-3.73</v>
       </c>
       <c r="L11" t="n">
         <v>8.85</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.28</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42681</v>
+        <v>42682</v>
       </c>
       <c r="H12" t="n">
-        <v>383.75</v>
+        <v>374.65</v>
       </c>
       <c r="I12" t="n">
         <v>378.356407125194</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K12" t="n">
-        <v>16.93</v>
+        <v>14.15</v>
       </c>
       <c r="L12" t="n">
         <v>1.48</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>15.07</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42740</v>
+        <v>42741</v>
       </c>
       <c r="H13" t="n">
-        <v>367.1</v>
+        <v>379.45</v>
       </c>
       <c r="I13" t="n">
         <v>376.5698190148713</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K13" t="n">
-        <v>2.02</v>
+        <v>-1.28</v>
       </c>
       <c r="L13" t="n">
         <v>11.2</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.47</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H14" t="n">
-        <v>458.55</v>
+        <v>440.85</v>
       </c>
       <c r="I14" t="n">
         <v>449.1075661595272</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K14" t="n">
-        <v>20.85</v>
+        <v>16.18</v>
       </c>
       <c r="L14" t="n">
         <v>13.19</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>11.9</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42887</v>
+        <v>42888</v>
       </c>
       <c r="H15" t="n">
-        <v>470.95</v>
+        <v>494.2</v>
       </c>
       <c r="I15" t="n">
         <v>481.4403693318533</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.83</v>
+        <v>-12.1</v>
       </c>
       <c r="L15" t="n">
-        <v>8.52</v>
+        <v>14.55</v>
       </c>
       <c r="M15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>4.04</v>
+        <v>4.94</v>
       </c>
       <c r="O15" t="n">
         <v>-3.86</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>13.14</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42955</v>
+        <v>42956</v>
       </c>
       <c r="H16" t="n">
-        <v>530</v>
+        <v>485.45</v>
       </c>
       <c r="I16" t="n">
         <v>501.4349076273249</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K16" t="n">
-        <v>7.24</v>
+        <v>-1.77</v>
       </c>
       <c r="L16" t="n">
         <v>4.37</v>
@@ -1353,7 +1544,7 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>3.51</v>
+        <v>8.41</v>
       </c>
       <c r="O16" t="n">
         <v>4.94</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>15.01</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43104</v>
+        <v>43105</v>
       </c>
       <c r="H17" t="n">
-        <v>431.5</v>
+        <v>440.2</v>
       </c>
       <c r="I17" t="n">
         <v>439.225950690558</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K17" t="n">
-        <v>11.11</v>
+        <v>9.32</v>
       </c>
       <c r="L17" t="n">
         <v>9.140000000000001</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.09</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43131</v>
+        <v>43132</v>
       </c>
       <c r="H18" t="n">
-        <v>425.8</v>
+        <v>417.65</v>
       </c>
       <c r="I18" t="n">
         <v>417.882777556694</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.27</v>
+        <v>-5.12</v>
       </c>
       <c r="L18" t="n">
         <v>5.94</v>
@@ -1467,7 +1682,7 @@
         <v>0.43</v>
       </c>
       <c r="N18" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
         <v>2.02</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.69</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43213</v>
+        <v>43214</v>
       </c>
       <c r="H19" t="n">
-        <v>398.95</v>
+        <v>404.9</v>
       </c>
       <c r="I19" t="n">
         <v>402.7222816844636</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K19" t="n">
-        <v>4.48</v>
+        <v>3.05</v>
       </c>
       <c r="L19" t="n">
         <v>3.93</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>7.44</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43237</v>
+        <v>43238</v>
       </c>
       <c r="H20" t="n">
-        <v>386.95</v>
+        <v>369.7</v>
       </c>
       <c r="I20" t="n">
         <v>382.1188591464446</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.43</v>
+        <v>-8.69</v>
       </c>
       <c r="L20" t="n">
-        <v>6.57</v>
+        <v>10.94</v>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.09</v>
+        <v>4.46</v>
       </c>
       <c r="O20" t="n">
         <v>1.49</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.62</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43263</v>
+        <v>43264</v>
       </c>
       <c r="H21" t="n">
-        <v>380.2</v>
+        <v>393.8</v>
       </c>
       <c r="I21" t="n">
         <v>387.5364632247475</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.84</v>
+        <v>-6.52</v>
       </c>
       <c r="L21" t="n">
         <v>10.37</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>11.8</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43278</v>
+        <v>43279</v>
       </c>
       <c r="H22" t="n">
-        <v>388.85</v>
+        <v>378.05</v>
       </c>
       <c r="I22" t="n">
         <v>379.0820493536094</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.26</v>
+        <v>-4</v>
       </c>
       <c r="L22" t="n">
-        <v>2.89</v>
+        <v>4.75</v>
       </c>
       <c r="M22" t="n">
         <v>1.18</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>13.57</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43329</v>
+        <v>43332</v>
       </c>
       <c r="H23" t="n">
-        <v>357.25</v>
+        <v>377.45</v>
       </c>
       <c r="I23" t="n">
         <v>376.318984471834</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K23" t="n">
-        <v>5.5</v>
+        <v>0.16</v>
       </c>
       <c r="L23" t="n">
         <v>5.79</v>
@@ -1752,7 +2027,7 @@
         <v>2.07</v>
       </c>
       <c r="N23" t="n">
-        <v>5.01</v>
+        <v>5.65</v>
       </c>
       <c r="O23" t="n">
         <v>-2.78</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>13.17</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43390</v>
+        <v>43392</v>
       </c>
       <c r="H24" t="n">
-        <v>377.55</v>
+        <v>371.75</v>
       </c>
       <c r="I24" t="n">
         <v>373.7823930072753</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K24" t="n">
-        <v>0.03</v>
+        <v>-1.51</v>
       </c>
       <c r="L24" t="n">
         <v>5.06</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.65</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H25" t="n">
-        <v>324.95</v>
+        <v>332.85</v>
       </c>
       <c r="I25" t="n">
         <v>332.5932485752673</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K25" t="n">
-        <v>12.59</v>
+        <v>10.46</v>
       </c>
       <c r="L25" t="n">
         <v>2.46</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43585</v>
+        <v>43587</v>
       </c>
       <c r="H26" t="n">
-        <v>325.45</v>
+        <v>314.9</v>
       </c>
       <c r="I26" t="n">
         <v>320.1564813996391</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.22</v>
+        <v>-5.39</v>
       </c>
       <c r="L26" t="n">
-        <v>3.71</v>
+        <v>5.9</v>
       </c>
       <c r="M26" t="n">
         <v>1.34</v>
       </c>
       <c r="N26" t="n">
-        <v>1.77</v>
+        <v>3.24</v>
       </c>
       <c r="O26" t="n">
         <v>2.43</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.6</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43713</v>
+        <v>43714</v>
       </c>
       <c r="H27" t="n">
-        <v>236.05</v>
+        <v>238.8</v>
       </c>
       <c r="I27" t="n">
         <v>238.6194611951507</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K27" t="n">
-        <v>25.04</v>
+        <v>24.17</v>
       </c>
       <c r="L27" t="n">
         <v>2.99</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>11.01</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43776</v>
+        <v>43777</v>
       </c>
       <c r="H28" t="n">
-        <v>234.9</v>
+        <v>232.4</v>
       </c>
       <c r="I28" t="n">
         <v>233.735739104409</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.63</v>
+        <v>-2.68</v>
       </c>
       <c r="L28" t="n">
         <v>6.22</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>12.42</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43789</v>
+        <v>43790</v>
       </c>
       <c r="H29" t="n">
-        <v>249.45</v>
+        <v>254.4</v>
       </c>
       <c r="I29" t="n">
         <v>253.5159779434372</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.34</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>8.41</v>
+        <v>10.11</v>
       </c>
       <c r="M29" t="n">
         <v>0.85</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>11.84</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43889</v>
+        <v>43892</v>
       </c>
       <c r="H30" t="n">
-        <v>260.05</v>
+        <v>250.15</v>
       </c>
       <c r="I30" t="n">
         <v>256.4584405726649</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K30" t="n">
-        <v>2.22</v>
+        <v>-1.67</v>
       </c>
       <c r="L30" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="M30" t="n">
         <v>1.15</v>
       </c>
       <c r="N30" t="n">
-        <v>3.43</v>
+        <v>3.81</v>
       </c>
       <c r="O30" t="n">
         <v>1.98</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>13.4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43909</v>
+        <v>43910</v>
       </c>
       <c r="H31" t="n">
-        <v>245.85</v>
+        <v>285.8</v>
       </c>
       <c r="I31" t="n">
         <v>280.2799717060143</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K31" t="n">
-        <v>1.72</v>
+        <v>-14.25</v>
       </c>
       <c r="L31" t="n">
-        <v>9.029999999999999</v>
+        <v>15.93</v>
       </c>
       <c r="M31" t="n">
-        <v>0.92</v>
+        <v>2.5</v>
       </c>
       <c r="N31" t="n">
-        <v>6.18</v>
+        <v>16.25</v>
       </c>
       <c r="O31" t="n">
         <v>-3.81</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>27.49</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H32" t="n">
-        <v>370.4</v>
+        <v>364.6</v>
       </c>
       <c r="I32" t="n">
         <v>365.9683973512794</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K32" t="n">
-        <v>29.6</v>
+        <v>27.57</v>
       </c>
       <c r="L32" t="n">
         <v>13.35</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>11.15</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44091</v>
+        <v>44092</v>
       </c>
       <c r="H33" t="n">
-        <v>393.7</v>
+        <v>409.7</v>
       </c>
       <c r="I33" t="n">
         <v>402.7511001947751</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.98</v>
+        <v>-12.37</v>
       </c>
       <c r="L33" t="n">
-        <v>8.779999999999999</v>
+        <v>16.02</v>
       </c>
       <c r="M33" t="n">
         <v>0.76</v>
       </c>
       <c r="N33" t="n">
-        <v>3.56</v>
+        <v>4.06</v>
       </c>
       <c r="O33" t="n">
         <v>-1.57</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.47</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H34" t="n">
-        <v>462.3</v>
+        <v>451.5</v>
       </c>
       <c r="I34" t="n">
         <v>456.0500737819087</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K34" t="n">
-        <v>12.84</v>
+        <v>10.2</v>
       </c>
       <c r="L34" t="n">
         <v>8.68</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.43</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44291</v>
+        <v>44292</v>
       </c>
       <c r="H35" t="n">
-        <v>439.95</v>
+        <v>456.5</v>
       </c>
       <c r="I35" t="n">
         <v>455.1821984679936</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K35" t="n">
-        <v>2.56</v>
+        <v>-1.11</v>
       </c>
       <c r="L35" t="n">
         <v>8.289999999999999</v>
@@ -2436,7 +2855,7 @@
         <v>1.74</v>
       </c>
       <c r="N35" t="n">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="O35" t="n">
         <v>-2.34</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.82</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44400</v>
+        <v>44403</v>
       </c>
       <c r="H36" t="n">
-        <v>615.25</v>
+        <v>605.55</v>
       </c>
       <c r="I36" t="n">
         <v>608.5665363344906</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K36" t="n">
-        <v>34.78</v>
+        <v>32.65</v>
       </c>
       <c r="L36" t="n">
         <v>3.44</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>7.1</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H37" t="n">
-        <v>369.6</v>
+        <v>375.15</v>
       </c>
       <c r="I37" t="n">
         <v>374.6299827320378</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K37" t="n">
-        <v>38.96</v>
+        <v>38.05</v>
       </c>
       <c r="L37" t="n">
         <v>2.72</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>9</v>
+      </c>
+      <c r="U37" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>9.57</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H38" t="n">
-        <v>352.3</v>
+        <v>341.15</v>
       </c>
       <c r="I38" t="n">
         <v>343.0132688340151</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.09</v>
+        <v>-9.06</v>
       </c>
       <c r="L38" t="n">
-        <v>7.76</v>
+        <v>10.02</v>
       </c>
       <c r="M38" t="n">
         <v>0.76</v>
       </c>
       <c r="N38" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="O38" t="n">
         <v>1.5</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>10.24</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44701</v>
+        <v>44704</v>
       </c>
       <c r="H39" t="n">
-        <v>356.85</v>
+        <v>362.5</v>
       </c>
       <c r="I39" t="n">
         <v>357.3394669380991</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.6</v>
+        <v>-6.26</v>
       </c>
       <c r="L39" t="n">
-        <v>5.97</v>
+        <v>8.69</v>
       </c>
       <c r="M39" t="n">
-        <v>2.56</v>
+        <v>3.91</v>
       </c>
       <c r="N39" t="n">
         <v>5.34</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.41</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44727</v>
+        <v>44728</v>
       </c>
       <c r="H40" t="n">
-        <v>352.65</v>
+        <v>343.2</v>
       </c>
       <c r="I40" t="n">
         <v>349.6353373403246</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.72</v>
+        <v>-5.32</v>
       </c>
       <c r="L40" t="n">
-        <v>3.71</v>
+        <v>5.93</v>
       </c>
       <c r="M40" t="n">
         <v>1.94</v>
       </c>
       <c r="N40" t="n">
-        <v>2.07</v>
+        <v>2.68</v>
       </c>
       <c r="O40" t="n">
         <v>1.58</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.91</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44742</v>
+        <v>44743</v>
       </c>
       <c r="H41" t="n">
-        <v>357</v>
+        <v>361.3</v>
       </c>
       <c r="I41" t="n">
         <v>359.1032151906574</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.02</v>
+        <v>-5.27</v>
       </c>
       <c r="L41" t="n">
-        <v>4.72</v>
+        <v>6.08</v>
       </c>
       <c r="M41" t="n">
         <v>0.93</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.42</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44767</v>
+        <v>44768</v>
       </c>
       <c r="H42" t="n">
-        <v>347.3</v>
+        <v>342.55</v>
       </c>
       <c r="I42" t="n">
         <v>347.1236436153977</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.87</v>
+        <v>-5.19</v>
       </c>
       <c r="L42" t="n">
-        <v>4.33</v>
+        <v>5.9</v>
       </c>
       <c r="M42" t="n">
         <v>0.91</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>7.76</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44783</v>
+        <v>44784</v>
       </c>
       <c r="H43" t="n">
-        <v>364.55</v>
+        <v>381.7</v>
       </c>
       <c r="I43" t="n">
         <v>369.1268096443455</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.42</v>
+        <v>-11.43</v>
       </c>
       <c r="L43" t="n">
-        <v>7.2</v>
+        <v>11.78</v>
       </c>
       <c r="M43" t="n">
-        <v>0.36</v>
+        <v>1.22</v>
       </c>
       <c r="N43" t="n">
         <v>5.24</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.57</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44805</v>
+        <v>44806</v>
       </c>
       <c r="H44" t="n">
-        <v>372.5</v>
+        <v>368.7</v>
       </c>
       <c r="I44" t="n">
         <v>370.2002212273671</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.41</v>
+        <v>-3.41</v>
       </c>
       <c r="L44" t="n">
         <v>3.71</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44833</v>
+        <v>44834</v>
       </c>
       <c r="H45" t="n">
-        <v>382.85</v>
+        <v>386.9</v>
       </c>
       <c r="I45" t="n">
         <v>383.2055444320308</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.84</v>
+        <v>-4.94</v>
       </c>
       <c r="L45" t="n">
-        <v>4.94</v>
+        <v>5.29</v>
       </c>
       <c r="M45" t="n">
         <v>0.74</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44879</v>
+        <v>44880</v>
       </c>
       <c r="H46" t="n">
-        <v>423.8</v>
+        <v>416.75</v>
       </c>
       <c r="I46" t="n">
         <v>418.8194445177361</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K46" t="n">
-        <v>9.539999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="L46" t="n">
         <v>1.59</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.53</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44928</v>
+        <v>44929</v>
       </c>
       <c r="H47" t="n">
-        <v>420.1</v>
+        <v>424.65</v>
       </c>
       <c r="I47" t="n">
         <v>424.405965576272</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.8</v>
+        <v>-1.9</v>
       </c>
       <c r="L47" t="n">
         <v>3.18</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.28</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45064</v>
+        <v>45065</v>
       </c>
       <c r="H48" t="n">
-        <v>508.05</v>
+        <v>494.7</v>
       </c>
       <c r="I48" t="n">
         <v>495.9843026558934</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K48" t="n">
-        <v>19.64</v>
+        <v>16.5</v>
       </c>
       <c r="L48" t="n">
         <v>1.4</v>
@@ -3177,7 +3752,7 @@
         <v>1.13</v>
       </c>
       <c r="N48" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="O48" t="n">
         <v>1.08</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>8.93</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45091</v>
+        <v>45092</v>
       </c>
       <c r="H49" t="n">
-        <v>532.35</v>
+        <v>549.15</v>
       </c>
       <c r="I49" t="n">
         <v>538.6274696833689</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.61</v>
+        <v>-11.01</v>
       </c>
       <c r="L49" t="n">
-        <v>7.85</v>
+        <v>11.18</v>
       </c>
       <c r="M49" t="n">
         <v>1.21</v>
       </c>
       <c r="N49" t="n">
-        <v>2.84</v>
+        <v>3.16</v>
       </c>
       <c r="O49" t="n">
         <v>-2.63</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.86</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45169</v>
+        <v>45170</v>
       </c>
       <c r="H50" t="n">
-        <v>625.85</v>
+        <v>613.95</v>
       </c>
       <c r="I50" t="n">
         <v>618.4628232925745</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K50" t="n">
-        <v>13.97</v>
+        <v>11.8</v>
       </c>
       <c r="L50" t="n">
         <v>2.93</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.18</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H51" t="n">
-        <v>597.3</v>
+        <v>625.2</v>
       </c>
       <c r="I51" t="n">
         <v>606.632260407857</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K51" t="n">
-        <v>2.71</v>
+        <v>-1.83</v>
       </c>
       <c r="L51" t="n">
         <v>6.51</v>
@@ -3348,7 +3959,7 @@
         <v>1.05</v>
       </c>
       <c r="N51" t="n">
-        <v>2.47</v>
+        <v>4.67</v>
       </c>
       <c r="O51" t="n">
         <v>-1.9</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="H52" t="n">
-        <v>937</v>
+        <v>922.15</v>
       </c>
       <c r="I52" t="n">
         <v>928.1362813639574</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K52" t="n">
-        <v>49.87</v>
+        <v>47.5</v>
       </c>
       <c r="L52" t="n">
         <v>4.34</v>
       </c>
       <c r="M52" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="N52" t="n">
         <v>3.22</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>8.76</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="H53" t="n">
-        <v>997.4</v>
+        <v>1020.75</v>
       </c>
       <c r="I53" t="n">
         <v>1002.952172498591</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K53" t="n">
-        <v>-8.16</v>
+        <v>-10.69</v>
       </c>
       <c r="L53" t="n">
-        <v>8.42</v>
+        <v>11.45</v>
       </c>
       <c r="M53" t="n">
         <v>1.52</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.9</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45442</v>
+        <v>45443</v>
       </c>
       <c r="H54" t="n">
-        <v>1023.95</v>
+        <v>1000.15</v>
       </c>
       <c r="I54" t="n">
         <v>1007.13634352185</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K54" t="n">
-        <v>0.31</v>
+        <v>-2.02</v>
       </c>
       <c r="L54" t="n">
         <v>5.46</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>11.96</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45476</v>
+        <v>45477</v>
       </c>
       <c r="H55" t="n">
-        <v>1095.25</v>
+        <v>1137.05</v>
       </c>
       <c r="I55" t="n">
         <v>1119.801436136048</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K55" t="n">
-        <v>-9.51</v>
+        <v>-13.69</v>
       </c>
       <c r="L55" t="n">
-        <v>11.48</v>
+        <v>14.47</v>
       </c>
       <c r="M55" t="n">
         <v>4.48</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.28</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45516</v>
+        <v>45517</v>
       </c>
       <c r="H56" t="n">
-        <v>1250.4</v>
+        <v>1175.45</v>
       </c>
       <c r="I56" t="n">
         <v>1195.215140072401</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K56" t="n">
-        <v>9.970000000000001</v>
+        <v>3.38</v>
       </c>
       <c r="L56" t="n">
         <v>3.85</v>
@@ -3633,7 +4304,7 @@
         <v>3.19</v>
       </c>
       <c r="N56" t="n">
-        <v>3.88</v>
+        <v>5.99</v>
       </c>
       <c r="O56" t="n">
         <v>3.82</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>14.84</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H57" t="n">
-        <v>981.45</v>
+        <v>1010.5</v>
       </c>
       <c r="I57" t="n">
         <v>1010.099974679965</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K57" t="n">
-        <v>16.5</v>
+        <v>14.03</v>
       </c>
       <c r="L57" t="n">
         <v>7.02</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>6</v>
+      </c>
+      <c r="U57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45681</v>
+        <v>45684</v>
       </c>
       <c r="H58" t="n">
-        <v>957.6</v>
+        <v>922.6</v>
       </c>
       <c r="I58" t="n">
         <v>928.7659433457791</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.24</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>5.49</v>
+        <v>9.4</v>
       </c>
       <c r="M58" t="n">
         <v>1.42</v>
       </c>
       <c r="N58" t="n">
-        <v>3.19</v>
+        <v>3.65</v>
       </c>
       <c r="O58" t="n">
         <v>2.96</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>10.16</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45693</v>
+        <v>45694</v>
       </c>
       <c r="H59" t="n">
-        <v>977</v>
+        <v>1008.2</v>
       </c>
       <c r="I59" t="n">
         <v>990.7777667333709</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.9</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>6.95</v>
+        <v>11.27</v>
       </c>
       <c r="M59" t="n">
-        <v>0.47</v>
+        <v>0.72</v>
       </c>
       <c r="N59" t="n">
-        <v>2.41</v>
+        <v>3.19</v>
       </c>
       <c r="O59" t="n">
         <v>-3.65</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H60" t="n">
-        <v>942.85</v>
+        <v>901.85</v>
       </c>
       <c r="I60" t="n">
         <v>914.1676377494546</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.48</v>
+        <v>-10.55</v>
       </c>
       <c r="L60" t="n">
-        <v>8.69</v>
+        <v>11.02</v>
       </c>
       <c r="M60" t="n">
         <v>-0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.97</v>
+        <v>4.35</v>
       </c>
       <c r="O60" t="n">
         <v>3.19</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>12.48</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="H61" t="n">
-        <v>926.4</v>
+        <v>931.5</v>
       </c>
       <c r="I61" t="n">
         <v>930.506526843249</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.72</v>
+        <v>-3.29</v>
       </c>
       <c r="L61" t="n">
         <v>5.3</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.5</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="H62" t="n">
-        <v>970</v>
+        <v>956.75</v>
       </c>
       <c r="I62" t="n">
         <v>957.6298182922072</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K62" t="n">
-        <v>4.13</v>
+        <v>2.71</v>
       </c>
       <c r="L62" t="n">
         <v>0.48</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.96</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45891</v>
+        <v>45894</v>
       </c>
       <c r="H63" t="n">
-        <v>988.8</v>
+        <v>1023.15</v>
       </c>
       <c r="I63" t="n">
         <v>994.2030587572692</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.35</v>
+        <v>-6.94</v>
       </c>
       <c r="L63" t="n">
-        <v>4.82</v>
+        <v>7.6</v>
       </c>
       <c r="M63" t="n">
         <v>0.63</v>
       </c>
       <c r="N63" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="O63" t="n">
         <v>-1.37</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>7.86</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H64" t="n">
-        <v>1019.25</v>
+        <v>975</v>
       </c>
       <c r="I64" t="n">
         <v>987.9925314589691</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.38</v>
+        <v>-4.71</v>
       </c>
       <c r="L64" t="n">
         <v>5.35</v>
       </c>
       <c r="M64" t="n">
-        <v>0.8</v>
+        <v>2.26</v>
       </c>
       <c r="N64" t="n">
-        <v>3.45</v>
+        <v>4.34</v>
       </c>
       <c r="O64" t="n">
         <v>3.47</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.42</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="H65" t="n">
-        <v>919.65</v>
+        <v>938.5</v>
       </c>
       <c r="I65" t="n">
         <v>923.7441564558809</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K65" t="n">
-        <v>5.68</v>
+        <v>3.74</v>
       </c>
       <c r="L65" t="n">
         <v>4.32</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>7</v>
+      </c>
+      <c r="U65" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.32</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="H66" t="n">
-        <v>899.6</v>
+        <v>876.15</v>
       </c>
       <c r="I66" t="n">
         <v>879.1744529555344</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.14</v>
+        <v>-6.64</v>
       </c>
       <c r="L66" t="n">
-        <v>6.54</v>
+        <v>6.87</v>
       </c>
       <c r="M66" t="n">
         <v>3.04</v>
       </c>
       <c r="N66" t="n">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="O66" t="n">
         <v>2.05</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H67" t="n">
-        <v>922.4</v>
+        <v>936.05</v>
       </c>
       <c r="I67" t="n">
         <v>928.6557433979781</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.28</v>
+        <v>-6.84</v>
       </c>
       <c r="L67" t="n">
-        <v>6.2</v>
+        <v>7.06</v>
       </c>
       <c r="M67" t="n">
         <v>2.69</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H68" t="n">
-        <v>1153</v>
+        <v>1112</v>
       </c>
       <c r="I68" t="n">
         <v>1131.00748445048</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K68" t="n">
-        <v>23.18</v>
+        <v>18.8</v>
       </c>
       <c r="L68" t="n">
         <v>4.88</v>
@@ -4317,7 +5132,7 @@
         <v>1.56</v>
       </c>
       <c r="N68" t="n">
-        <v>3.21</v>
+        <v>3.56</v>
       </c>
       <c r="O68" t="n">
         <v>1.48</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>7</v>
+      </c>
+      <c r="U68" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>14</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9335,7 +10170,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.5</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="6">
@@ -9345,7 +10180,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -9355,7 +10190,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8">
@@ -9365,7 +10200,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9375,7 +10210,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95.5</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="10">
@@ -9385,7 +10220,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143.2</v>
+        <v>145.4</v>
       </c>
     </row>
     <row r="11">
@@ -9425,7 +10260,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.81</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="15">
@@ -9435,7 +10270,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.27</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="16">
@@ -9445,7 +10280,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.26</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="17">
@@ -9455,7 +10290,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49.87</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="18">
@@ -9465,7 +10300,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.3</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="19">
@@ -9475,7 +10310,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.01</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="20">
@@ -9485,7 +10320,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.79</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="21">
@@ -9495,7 +10330,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.35</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="22">
@@ -9505,7 +10340,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -9515,7 +10350,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -9525,7 +10360,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="25">
@@ -9545,7 +10380,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.86</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="27">
@@ -9555,7 +10390,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.98</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="28">
@@ -9565,7 +10400,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
